--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BAUBLOCK GYMNÁSTICA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BAUBLOCK GYMNÁSTICA.xlsx
@@ -565,73 +565,73 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9.510300000000001</v>
+        <v>9.610799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0371</v>
+        <v>11.7645</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5268</v>
+        <v>-2.1536</v>
       </c>
       <c r="G2" t="n">
-        <v>9.992799999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7371</v>
+        <v>2.6334</v>
       </c>
       <c r="I2" t="n">
-        <v>7.255800000000001</v>
+        <v>7.2667</v>
       </c>
       <c r="J2" t="n">
-        <v>12.1927</v>
+        <v>12.6166</v>
       </c>
       <c r="K2" t="n">
-        <v>4.782299999999999</v>
+        <v>4.9726</v>
       </c>
       <c r="L2" t="n">
-        <v>7.410399999999999</v>
+        <v>7.6441</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1998</v>
+        <v>-2.7165</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0452</v>
+        <v>-2.3392</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1546</v>
+        <v>-0.3773</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.4015</v>
+        <v>-5.257899999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4006</v>
+        <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0007</v>
+        <v>-0.9798</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1474</v>
+        <v>1.1767</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.1481</v>
+        <v>-2.1566</v>
       </c>
       <c r="V2" t="n">
-        <v>3.519</v>
+        <v>3.6116</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0986</v>
+        <v>3.2289</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7996</v>
+        <v>1.9347</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7996</v>
+        <v>1.4942</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.4405</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7996</v>
+        <v>4.15</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5998</v>
+        <v>5.2735</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1998</v>
+        <v>-1.1234</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7996</v>
+        <v>5.6087</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5998</v>
+        <v>7.431100000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1998</v>
+        <v>-1.8225</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1.4586</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-2.1577</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.6990000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-5.8421</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.3369</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.0364000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.1061</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.06970000000000004</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.6632</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.1706</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5074000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4181</v>
+        <v>1.8316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1873</v>
+        <v>1.8316</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2307</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8114</v>
+        <v>1.8316</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9157</v>
+        <v>0.6158</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1042</v>
+        <v>1.2158</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7263</v>
+        <v>1.8316</v>
       </c>
       <c r="K4" t="n">
-        <v>6.747</v>
+        <v>0.6158</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.0207</v>
+        <v>1.2158</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9149</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8314</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9165000000000001</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.0017</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.4024</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4007</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009000000000000008</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1751</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1843</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5993</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.0386</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0214</v>
+        <v>-0.037</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1328</v>
+        <v>1.1776</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1543</v>
+        <v>-1.2146</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0599</v>
+        <v>-0.0711</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6442</v>
+        <v>-0.6676</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5843</v>
+        <v>0.5966</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2617</v>
+        <v>1.3013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2417</v>
+        <v>1.2808</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3216</v>
+        <v>-1.3723</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6574</v>
+        <v>-0.6842</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0384</v>
+        <v>0.0341</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1673</v>
+        <v>0.1577</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3097000000000001</v>
+        <v>-0.4098000000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1105</v>
+        <v>-0.9386</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8008000000000001</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2183999999999999</v>
+        <v>-0.3403999999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0964</v>
+        <v>-1.2075</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8779999999999999</v>
+        <v>0.8671</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6616</v>
+        <v>1.7186</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9398</v>
+        <v>0.9648000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7218</v>
+        <v>0.7539</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.88</v>
+        <v>-2.0591</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0361</v>
+        <v>-2.1723</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1562</v>
+        <v>0.1132</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6912</v>
+        <v>-0.6799000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8313</v>
+        <v>-0.7946</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1401</v>
+        <v>0.1147</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5999</v>
+        <v>0.6106</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3824999999999998</v>
+        <v>-0.5005999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>5.7549</v>
+        <v>6.249300000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.1373</v>
+        <v>-6.7499</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9507</v>
+        <v>1.9974</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1546</v>
+        <v>1.2357</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7960999999999999</v>
+        <v>0.7617</v>
       </c>
       <c r="J7" t="n">
-        <v>5.0971</v>
+        <v>5.5023</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6916</v>
+        <v>4.0106</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4055</v>
+        <v>1.4918</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1465</v>
+        <v>-3.505</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.537</v>
+        <v>-2.7749</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6093999999999999</v>
+        <v>-0.7301</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001000000000001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8008</v>
+        <v>2.7264</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4059</v>
+        <v>2.3278</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1987</v>
+        <v>2.1938</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2072</v>
+        <v>0.134</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.1391</v>
+        <v>-5.2153</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.9988</v>
+        <v>-6.1053</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6717</v>
+        <v>-0.7326</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2468</v>
+        <v>-0.2289</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.425</v>
+        <v>-0.5036999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6392</v>
+        <v>-0.6986000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.373</v>
+        <v>-0.4018</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2662</v>
+        <v>-0.2968</v>
       </c>
       <c r="J8" t="n">
-        <v>0.14</v>
+        <v>0.1421</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7792</v>
+        <v>-0.8407</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.393</v>
+        <v>-0.4224000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3868</v>
+        <v>-0.371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3542</v>
+        <v>0.337</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8811</v>
+        <v>-1.8828</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7987</v>
+        <v>-1.4924</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08240000000000003</v>
+        <v>-0.3904</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0179</v>
+        <v>-2.5305</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7808</v>
+        <v>-2.8727</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7629</v>
+        <v>0.3421000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3831</v>
+        <v>-0.7675000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3925999999999999</v>
+        <v>-0.8569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009500000000000064</v>
+        <v>0.08940000000000003</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3652</v>
+        <v>-1.7631</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3882</v>
+        <v>-2.0158</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7534000000000001</v>
+        <v>0.2527</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2000000000000001</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.4004</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2004</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3434</v>
+        <v>-0.2101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.01519999999999988</v>
+        <v>-0.4143</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.3282</v>
+        <v>0.2042</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6802</v>
+        <v>1.8316</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8316</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8956</v>
+        <v>-1.9983</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6911</v>
+        <v>-1.4846</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2045</v>
+        <v>-0.5137</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4818</v>
+        <v>-0.1754</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8105</v>
+        <v>-0.8899</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3287</v>
+        <v>0.7146</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8523000000000001</v>
+        <v>-0.1548</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8960999999999999</v>
+        <v>-0.277</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04380000000000006</v>
+        <v>0.1221999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6295</v>
+        <v>-0.02060000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9144</v>
+        <v>-0.6129</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2849</v>
+        <v>0.5923</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0003</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2006</v>
+        <v>-1.3632</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2132</v>
+        <v>-2.2903</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4378</v>
+        <v>0.03330000000000011</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2246</v>
+        <v>-2.3236</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7997</v>
+        <v>0.6621</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6346</v>
+        <v>-2.8281</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8066</v>
+        <v>2.2613</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4412</v>
+        <v>-5.0894</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3448</v>
+        <v>1.1598</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1263</v>
+        <v>-2.1639</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4711</v>
+        <v>3.3237</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4161</v>
+        <v>2.7158</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5454000000000001</v>
+        <v>-0.3076</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9615</v>
+        <v>3.0234</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0713</v>
+        <v>-1.556</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5809</v>
+        <v>-1.8564</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5097</v>
+        <v>0.3003</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2000999999999999</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.6008</v>
+        <v>-2.5316</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4007</v>
+        <v>2.3369</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0396</v>
+        <v>-1.0199</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2119</v>
+        <v>1.2386</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.2515</v>
+        <v>-2.2586</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7397</v>
+        <v>-2.7732</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7793999999999999</v>
+        <v>0.8385</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.519</v>
+        <v>-3.6116</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6944</v>
+        <v>-4.714399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5932</v>
+        <v>-4.2013</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1012000000000002</v>
+        <v>-0.5131000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1455</v>
+        <v>-2.2431</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8032</v>
+        <v>-1.9142</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3423999999999998</v>
+        <v>-0.329</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2627</v>
+        <v>-2.0737</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7943</v>
+        <v>-0.7209</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4684</v>
+        <v>-1.3529</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1172</v>
+        <v>-0.1694000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0087</v>
+        <v>-1.1932</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1259</v>
+        <v>1.0238</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8005</v>
+        <v>-1.7527</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4004</v>
+        <v>1.3631</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0082</v>
+        <v>-0.9981</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8489</v>
+        <v>-0.7919</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1592</v>
+        <v>-0.2064</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5006</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.568300000000001</v>
+        <v>-6.614100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7641</v>
+        <v>-2.5974</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8041</v>
+        <v>-4.0168</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0978</v>
+        <v>-1.104</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7377</v>
+        <v>-1.7525</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6399</v>
+        <v>0.6484</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7324999999999999</v>
+        <v>-0.6343</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6943999999999999</v>
+        <v>-0.6182</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0381</v>
+        <v>-0.0161</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3653</v>
+        <v>-0.4696</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0433</v>
+        <v>-1.1341</v>
       </c>
       <c r="O13" t="n">
-        <v>0.678</v>
+        <v>0.6645</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2000999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0711</v>
+        <v>-1.0417</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8312999999999999</v>
+        <v>-0.7946</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.24</v>
+        <v>-0.2471</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.3313</v>
+        <v>-6.340600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.5139</v>
+        <v>13.8353</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.8453</v>
+        <v>-20.1759</v>
       </c>
       <c r="G14" t="n">
-        <v>12.2388</v>
+        <v>11.8757</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.964899999999999</v>
+        <v>-2.111699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>14.2038</v>
+        <v>13.9875</v>
       </c>
       <c r="J14" t="n">
-        <v>25.0645</v>
+        <v>27.8067</v>
       </c>
       <c r="K14" t="n">
-        <v>13.4777</v>
+        <v>15.2553</v>
       </c>
       <c r="L14" t="n">
-        <v>11.5868</v>
+        <v>12.5515</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.8257</v>
+        <v>-15.9309</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.4424</v>
+        <v>-17.3671</v>
       </c>
       <c r="O14" t="n">
-        <v>2.617</v>
+        <v>1.4358</v>
       </c>
       <c r="P14" t="n">
-        <v>-12.0035</v>
+        <v>-11.6842</v>
       </c>
       <c r="Q14" t="n">
-        <v>-29.0082</v>
+        <v>-28.2368</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0048</v>
+        <v>16.5527</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.9465</v>
+        <v>-4.9283</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9026999999999996</v>
+        <v>1.2462</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.849299999999999</v>
+        <v>-6.175</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.620100000000001</v>
+        <v>-1.603600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>12.5552</v>
+        <v>13.0191</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.1752</v>
+        <v>-14.6228</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BAUBLOCK GYMNÁSTICA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BAUBLOCK GYMNÁSTICA.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9.610799999999999</v>
+        <v>10.0128</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7645</v>
+        <v>11.3657</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1536</v>
+        <v>-1.353</v>
       </c>
       <c r="G2" t="n">
         <v>9.9</v>
@@ -610,13 +610,13 @@
         <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9798</v>
+        <v>-0.5778000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1767</v>
+        <v>0.778</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.1566</v>
+        <v>-1.3558</v>
       </c>
       <c r="V2" t="n">
         <v>3.6116</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9347</v>
+        <v>1.8316</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4942</v>
+        <v>1.8316</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4405</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.15</v>
+        <v>1.8316</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2735</v>
+        <v>0.6158</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1234</v>
+        <v>1.2158</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6087</v>
+        <v>1.8316</v>
       </c>
       <c r="K3" t="n">
-        <v>7.431100000000001</v>
+        <v>0.6158</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.8225</v>
+        <v>1.2158</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4586</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1577</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6990000000000001</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.8421</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-8.178900000000001</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3369</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0364000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1061</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06970000000000004</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6632</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1706</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5074000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8316</v>
+        <v>1.4824</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8316</v>
+        <v>1.8551</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.3726</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8316</v>
+        <v>4.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6158</v>
+        <v>5.2735</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2158</v>
+        <v>-1.1234</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8316</v>
+        <v>5.6087</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6158</v>
+        <v>7.431100000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2158</v>
+        <v>-1.8225</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.4586</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.1577</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.6990000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-5.8421</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3369</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.4887</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.2547</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.7435</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.6632</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.1706</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5074000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.037</v>
+        <v>0.1719999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1776</v>
+        <v>-0.4402</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2146</v>
+        <v>0.6122000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0711</v>
+        <v>-0.3403999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6676</v>
+        <v>-1.2075</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5966</v>
+        <v>0.8671</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3013</v>
+        <v>1.7186</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0205</v>
+        <v>0.9648000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2808</v>
+        <v>0.7539</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3723</v>
+        <v>-2.0591</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6882</v>
+        <v>-2.1723</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6842</v>
+        <v>0.1132</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0341</v>
+        <v>-0.09810000000000002</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1237</v>
+        <v>-0.2962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1577</v>
+        <v>0.1981</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6106</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4098000000000002</v>
+        <v>-0.0648</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9386</v>
+        <v>1.1776</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5287999999999999</v>
+        <v>-1.2424</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3403999999999998</v>
+        <v>-0.0711</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2075</v>
+        <v>-0.6676</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8671</v>
+        <v>0.5966</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7186</v>
+        <v>1.3013</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9648000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7539</v>
+        <v>1.2808</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0591</v>
+        <v>-1.3723</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1723</v>
+        <v>-0.6882</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1132</v>
+        <v>-0.6842</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1421</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1421</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6799000000000001</v>
+        <v>0.0062</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7946</v>
+        <v>-0.1237</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1147</v>
+        <v>0.1299</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6106</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5005999999999999</v>
+        <v>-0.6151</v>
       </c>
       <c r="E7" t="n">
-        <v>6.249300000000001</v>
+        <v>-0.1671</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.7499</v>
+        <v>-0.448</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9974</v>
+        <v>-0.6986000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2357</v>
+        <v>-0.4018</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7617</v>
+        <v>-0.2968</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5023</v>
+        <v>0.1421</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0106</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4918</v>
+        <v>0.1216</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.505</v>
+        <v>-0.8407</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.7749</v>
+        <v>-0.4224000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7301</v>
+        <v>-0.4184</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3368</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7264</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3278</v>
+        <v>0.0835</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1938</v>
+        <v>-0.3092</v>
       </c>
       <c r="U7" t="n">
-        <v>0.134</v>
+        <v>0.3927</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.2153</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.1053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7326</v>
+        <v>-1.0153</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2289</v>
+        <v>-1.0241</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5036999999999999</v>
+        <v>0.008799999999999975</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6986000000000001</v>
+        <v>-0.1754</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4018</v>
+        <v>-0.8899</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2968</v>
+        <v>0.7146</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1421</v>
+        <v>-0.1548</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>-0.277</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1216</v>
+        <v>0.1221999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8407</v>
+        <v>-0.02060000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4224000000000001</v>
+        <v>-0.6129</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4184</v>
+        <v>0.5923</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3632</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.034</v>
+        <v>-1.3073</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.371</v>
+        <v>0.4938</v>
       </c>
       <c r="U8" t="n">
-        <v>0.337</v>
+        <v>-1.8011</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8828</v>
+        <v>-1.301</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4924</v>
+        <v>-0.9941000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3904</v>
+        <v>-0.3069000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5305</v>
@@ -1156,13 +1156,13 @@
         <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2101</v>
+        <v>0.3717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4143</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2042</v>
+        <v>0.2877</v>
       </c>
       <c r="V9" t="n">
         <v>1.8316</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9983</v>
+        <v>-2.343</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4846</v>
+        <v>5.0532</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5137</v>
+        <v>-7.3962</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1754</v>
+        <v>1.9974</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8899</v>
+        <v>1.2357</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7146</v>
+        <v>0.7617</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1548</v>
+        <v>5.5023</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.277</v>
+        <v>4.0106</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1221999999999999</v>
+        <v>1.4918</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02060000000000001</v>
+        <v>-3.505</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6129</v>
+        <v>-2.7749</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5923</v>
+        <v>-0.7301</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3632</v>
+        <v>-2.3368</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1684</v>
+        <v>2.7264</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2903</v>
+        <v>0.4855</v>
       </c>
       <c r="T10" t="n">
-        <v>0.03330000000000011</v>
+        <v>0.9977</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.3236</v>
+        <v>-0.5123</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6621</v>
+        <v>-5.2153</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6621</v>
+        <v>-6.1053</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8281</v>
+        <v>-2.9639</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2613</v>
+        <v>1.4639</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0894</v>
+        <v>-4.427700000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1.1598</v>
@@ -1312,13 +1312,13 @@
         <v>2.3369</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0199</v>
+        <v>-1.1558</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2386</v>
+        <v>0.4411999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.2586</v>
+        <v>-1.5969</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7732</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.714399999999999</v>
+        <v>-4.393</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2013</v>
+        <v>-3.7408</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5131000000000001</v>
+        <v>-0.6522000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2431</v>
@@ -1390,13 +1390,13 @@
         <v>1.3631</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9981</v>
+        <v>-0.6768000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7919</v>
+        <v>-0.3313</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2064</v>
+        <v>-0.3455</v>
       </c>
       <c r="V12" t="n">
         <v>0.2795</v>
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.614100000000001</v>
+        <v>-6.1698</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5974</v>
+        <v>-2.2366</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0168</v>
+        <v>-3.9333</v>
       </c>
       <c r="G13" t="n">
         <v>-1.104</v>
@@ -1468,13 +1468,13 @@
         <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0417</v>
+        <v>-0.5973999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7946</v>
+        <v>-0.4337</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2471</v>
+        <v>-0.1636</v>
       </c>
       <c r="V13" t="n">
         <v>-4.2737</v>
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.340600000000001</v>
+        <v>-5.3671</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8353</v>
+        <v>14.1442</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.1759</v>
+        <v>-19.5113</v>
       </c>
       <c r="G14" t="n">
         <v>11.8757</v>
@@ -1519,7 +1519,7 @@
         <v>13.9875</v>
       </c>
       <c r="J14" t="n">
-        <v>27.8067</v>
+        <v>27.80670000000001</v>
       </c>
       <c r="K14" t="n">
         <v>15.2553</v>
@@ -1546,13 +1546,13 @@
         <v>16.5527</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.9283</v>
+        <v>-3.955</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2462</v>
+        <v>1.5553</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.175</v>
+        <v>-5.510300000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.603600000000001</v>
